--- a/tables/tabla-codices.xlsx
+++ b/tables/tabla-codices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Dropbox\HSMS-OSTA\Textos-OSTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C903EC67-8072-4C3F-AC1D-DF0593A94187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87BD29B-5894-425B-BE24-573C82380A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18630" yWindow="3075" windowWidth="27765" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3705" yWindow="2325" windowWidth="35400" windowHeight="15345" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tabla códices" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16488" uniqueCount="4640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16488" uniqueCount="4641">
   <si>
     <t>HSMS ID</t>
   </si>
@@ -13967,6 +13967,9 @@
   </si>
   <si>
     <t>La triste y dolorosa muerte de la princesa nuestra señora</t>
+  </si>
+  <si>
+    <t>INC/2553</t>
   </si>
 </sst>
 </file>
@@ -37994,7 +37997,7 @@
         <v>433</v>
       </c>
       <c r="F466" s="2" t="s">
-        <v>2928</v>
+        <v>4640</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>2929</v>
